--- a/xls_files/Football_WorldCupPredictions_Template.xlsx
+++ b/xls_files/Football_WorldCupPredictions_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a30912dd2cc41ecc/Terry Shared Documents/WorldCup2022/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paulio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268E9080-2328-4672-A8DA-DEFA38166D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E68101-82DC-4021-BFEC-FB203A629397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="16755" firstSheet="1" activeTab="1" xr2:uid="{02E04345-04C2-4539-8F12-CAD16CDA2800}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{02E04345-04C2-4539-8F12-CAD16CDA2800}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" state="hidden" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="236">
   <si>
     <t>Friday 11 June</t>
   </si>
@@ -279,30 +279,12 @@
     <t>Quarter Finals</t>
   </si>
   <si>
-    <t>QF1</t>
-  </si>
-  <si>
-    <t>QF2</t>
-  </si>
-  <si>
-    <t>QF3</t>
-  </si>
-  <si>
-    <t>QF4</t>
-  </si>
-  <si>
     <t>Semi Finals</t>
   </si>
   <si>
     <t>Finale</t>
   </si>
   <si>
-    <t>SF1</t>
-  </si>
-  <si>
-    <t>SF2</t>
-  </si>
-  <si>
     <t>Example</t>
   </si>
   <si>
@@ -321,9 +303,6 @@
     <t>7. An extra bonus point can be gained if the game goes to extra time, you select the team that goes through.  See example below.</t>
   </si>
   <si>
-    <t>World Cup 2022 Predictions</t>
-  </si>
-  <si>
     <t>Group Games</t>
   </si>
   <si>
@@ -336,12 +315,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>20 Nov 16:00</t>
-  </si>
-  <si>
-    <t>21 Nov 13:00</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -354,18 +327,12 @@
     <t>USA</t>
   </si>
   <si>
-    <t>22 Nov 10:00</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
     <t>D</t>
   </si>
   <si>
-    <t>22 Nov 13:00</t>
-  </si>
-  <si>
     <t>Argentina</t>
   </si>
   <si>
@@ -381,9 +348,6 @@
     <t>Australia</t>
   </si>
   <si>
-    <t>23 Nov 10:00</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -396,24 +360,15 @@
     <t>Japan</t>
   </si>
   <si>
-    <t>Costa Rica</t>
-  </si>
-  <si>
     <t>Canada</t>
   </si>
   <si>
-    <t>24 Nov 10:00</t>
-  </si>
-  <si>
     <t>G</t>
   </si>
   <si>
     <t>H</t>
   </si>
   <si>
-    <t>Cameroon</t>
-  </si>
-  <si>
     <t>Uruguay</t>
   </si>
   <si>
@@ -426,90 +381,6 @@
     <t>Brazil</t>
   </si>
   <si>
-    <t>Serbia</t>
-  </si>
-  <si>
-    <t>25 Nov 10:00</t>
-  </si>
-  <si>
-    <t>26 Nov 10:00</t>
-  </si>
-  <si>
-    <t>27 Nov 10:00</t>
-  </si>
-  <si>
-    <t>28 Nov 10:00</t>
-  </si>
-  <si>
-    <t>29 Nov 15:00</t>
-  </si>
-  <si>
-    <t>30 Nov 15:00</t>
-  </si>
-  <si>
-    <t>1 Dec 15:00</t>
-  </si>
-  <si>
-    <t>25 Nov 13:00</t>
-  </si>
-  <si>
-    <t>29 Nov 19:00</t>
-  </si>
-  <si>
-    <t>26 Nov 13:00</t>
-  </si>
-  <si>
-    <t>30 Nov 19:00</t>
-  </si>
-  <si>
-    <t>23 Nov 13:00</t>
-  </si>
-  <si>
-    <t>1 Dec 19:00</t>
-  </si>
-  <si>
-    <t>2 Dec 15:00</t>
-  </si>
-  <si>
-    <t>27 Nov 13:00</t>
-  </si>
-  <si>
-    <t>2 Dec 19:00</t>
-  </si>
-  <si>
-    <t>24 Nov 13:00</t>
-  </si>
-  <si>
-    <t>28 Nov 13:00</t>
-  </si>
-  <si>
-    <t>3 Dec 15:00</t>
-  </si>
-  <si>
-    <t>5 Dec 15:00</t>
-  </si>
-  <si>
-    <t>4 Dec 15:00</t>
-  </si>
-  <si>
-    <t>6 Dec 15:00</t>
-  </si>
-  <si>
-    <t>9 Dec 15:00</t>
-  </si>
-  <si>
-    <t>10 Dec 15:00</t>
-  </si>
-  <si>
-    <t>13 Dec 19:00</t>
-  </si>
-  <si>
-    <t>14 Dec 19:00</t>
-  </si>
-  <si>
-    <t>18 Dec 15:00</t>
-  </si>
-  <si>
     <t>5. All entries by 12:00 Saturday 3 December</t>
   </si>
   <si>
@@ -528,19 +399,376 @@
     <t>The pointless 3rd Place Game</t>
   </si>
   <si>
-    <t>17 Dec 15:00</t>
-  </si>
-  <si>
-    <t>21 Nov 16:00</t>
-  </si>
-  <si>
     <t>4. All entries by 12:00 Sunday 20 November</t>
   </si>
   <si>
-    <t>Paulio</t>
-  </si>
-  <si>
     <t>Here I've selected a Team A 3-1 win.  If this happens in 90 minutes, I would get 3 points.</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>World Cup 2026 Predictions</t>
+  </si>
+  <si>
+    <t>11 Jun 20:00</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>12 Jun 03:00</t>
+  </si>
+  <si>
+    <t>Bosnia</t>
+  </si>
+  <si>
+    <t>12 Jun 20:00</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>13 Jun 02:00</t>
+  </si>
+  <si>
+    <t>13 Jun 20:00</t>
+  </si>
+  <si>
+    <t>13 Jun 23:00</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>14 Jun 02:00</t>
+  </si>
+  <si>
+    <t>14 Jun 05:00</t>
+  </si>
+  <si>
+    <t>Curacao</t>
+  </si>
+  <si>
+    <t>14 Jun 18:00</t>
+  </si>
+  <si>
+    <t>14 Jun 9pm</t>
+  </si>
+  <si>
+    <t>Ivory Coast</t>
+  </si>
+  <si>
+    <t>15 Jun 00:00</t>
+  </si>
+  <si>
+    <t>15 Jun 03:00</t>
+  </si>
+  <si>
+    <t>Cape Verde</t>
+  </si>
+  <si>
+    <t>15 Jun 17:00</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>15 Jun 20:00</t>
+  </si>
+  <si>
+    <t>15 Jun 23:00</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>16 Jun 02:00</t>
+  </si>
+  <si>
+    <t>16 Jun 20:00</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
+    <t>17 Jun 02:00</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>DR Congo</t>
+  </si>
+  <si>
+    <t>17 Jun 18:00</t>
+  </si>
+  <si>
+    <t>17 Jun 21:00</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>18 Jun 00:00</t>
+  </si>
+  <si>
+    <t>Uzbekistan</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>18 Jun 03:00</t>
+  </si>
+  <si>
+    <t>18 Jun 17:00</t>
+  </si>
+  <si>
+    <t>18 Jun 20:00</t>
+  </si>
+  <si>
+    <t>19 Jun 02:00</t>
+  </si>
+  <si>
+    <t>19 Jun 20:00</t>
+  </si>
+  <si>
+    <t>19 Jun 23:00</t>
+  </si>
+  <si>
+    <t>20 Jun 01:30</t>
+  </si>
+  <si>
+    <t>20 Jun 04:00</t>
+  </si>
+  <si>
+    <t>20 Jun 18:00</t>
+  </si>
+  <si>
+    <t>20 Jun 21:00</t>
+  </si>
+  <si>
+    <t>21 Jun 01:00</t>
+  </si>
+  <si>
+    <t>21 Jun 05:00</t>
+  </si>
+  <si>
+    <t>21 Jun 17:00</t>
+  </si>
+  <si>
+    <t>21 Jun 20:00</t>
+  </si>
+  <si>
+    <t>21 Jun 23:00</t>
+  </si>
+  <si>
+    <t>22 Jun 02:00</t>
+  </si>
+  <si>
+    <t>22 Jun 18:00</t>
+  </si>
+  <si>
+    <t>22 Jun 22:00</t>
+  </si>
+  <si>
+    <t>23 Jun 01:00</t>
+  </si>
+  <si>
+    <t>23 Jun 04:00</t>
+  </si>
+  <si>
+    <t>23 Jun 18:00</t>
+  </si>
+  <si>
+    <t>23 Jun 21:00</t>
+  </si>
+  <si>
+    <t>24 Jun 00:00</t>
+  </si>
+  <si>
+    <t>24 Jun 03:00</t>
+  </si>
+  <si>
+    <t>24 Jun 20:00</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>24 Jun 23:00</t>
+  </si>
+  <si>
+    <t>25 Jun 02:00</t>
+  </si>
+  <si>
+    <t>25 Jun 21:00</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>26 Jun 00:00</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>26 Jun 03:00</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>26 Jun 20:00</t>
+  </si>
+  <si>
+    <t>27 Jun 01:00</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>27 Jun 04:00</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>27 Jun 22:00</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>28 Jun 00:30</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>28 Jun 03:00</t>
+  </si>
+  <si>
+    <t>Round of 32</t>
+  </si>
+  <si>
+    <t>28 Jun 20:00</t>
+  </si>
+  <si>
+    <t>29 Jun 21:30</t>
+  </si>
+  <si>
+    <t>30 Jun 02:00</t>
+  </si>
+  <si>
+    <t>29 Jun 18:00</t>
+  </si>
+  <si>
+    <t>30 Jun 22:00</t>
+  </si>
+  <si>
+    <t>30 Jun 18:00</t>
+  </si>
+  <si>
+    <t>1 Jul 02:00</t>
+  </si>
+  <si>
+    <t>1 Jul 17:00</t>
+  </si>
+  <si>
+    <t>2 Jul 01:00</t>
+  </si>
+  <si>
+    <t>1 Jul 21:00</t>
+  </si>
+  <si>
+    <t>3 Jul 00:00</t>
+  </si>
+  <si>
+    <t>2 Jul 20:00</t>
+  </si>
+  <si>
+    <t>3 Jul 04:00</t>
+  </si>
+  <si>
+    <t>3 Jul 23:00</t>
+  </si>
+  <si>
+    <t>4 Jul 02:30</t>
+  </si>
+  <si>
+    <t>3 Jul 19:00</t>
+  </si>
+  <si>
+    <t>4 Jul 22:00</t>
+  </si>
+  <si>
+    <t>4 Jul 18:00</t>
+  </si>
+  <si>
+    <t>5 Jul 21:00</t>
+  </si>
+  <si>
+    <t>6 Jul 01:00</t>
+  </si>
+  <si>
+    <t>6 Jul 20:00</t>
+  </si>
+  <si>
+    <t>7 Jul 01:00</t>
+  </si>
+  <si>
+    <t>7 Jul 17:00</t>
+  </si>
+  <si>
+    <t>7 Jul 21:00</t>
+  </si>
+  <si>
+    <t>9 Jul 21:00</t>
+  </si>
+  <si>
+    <t>10 Jul 20:00</t>
+  </si>
+  <si>
+    <t>11 Jul 22:00</t>
+  </si>
+  <si>
+    <t>12 Jul 22:00</t>
+  </si>
+  <si>
+    <t>14 Jul 20:00</t>
+  </si>
+  <si>
+    <t>15 Jul 20:00</t>
+  </si>
+  <si>
+    <t>18 Jul 22:00</t>
+  </si>
+  <si>
+    <t>19 Jul 20:00</t>
   </si>
 </sst>
 </file>
@@ -733,7 +961,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -768,25 +996,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -810,9 +1026,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -822,20 +1035,17 @@
     <xf numFmtId="20" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -845,6 +1055,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -864,9 +1086,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -904,7 +1126,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1010,7 +1232,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1152,7 +1374,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1181,13 +1403,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="8" t="s">
         <v>39</v>
       </c>
@@ -1206,14 +1428,14 @@
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="5" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
@@ -1226,18 +1448,18 @@
       <c r="E5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="16"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="37"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="31"/>
     </row>
     <row r="6" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I6" s="7" t="s">
@@ -1256,14 +1478,14 @@
       </c>
     </row>
     <row r="7" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
       <c r="I7" s="7" t="s">
         <v>63</v>
       </c>
@@ -1341,14 +1563,14 @@
       <c r="G10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="35" t="s">
+      <c r="I10" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="37"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="31"/>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I11" s="7" t="s">
@@ -1367,14 +1589,14 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
       <c r="I12" s="7" t="s">
         <v>65</v>
       </c>
@@ -1452,14 +1674,14 @@
       <c r="G15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="35" t="s">
+      <c r="I15" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="37"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="31"/>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I16" s="7" t="s">
@@ -1478,14 +1700,14 @@
       </c>
     </row>
     <row r="17" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
       <c r="I17" s="7" t="s">
         <v>67</v>
       </c>
@@ -1533,14 +1755,14 @@
       <c r="G19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I19" s="35" t="s">
+      <c r="I19" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="37"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="31"/>
     </row>
     <row r="20" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
@@ -1589,14 +1811,14 @@
       </c>
     </row>
     <row r="22" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
       <c r="I22" s="7" t="s">
         <v>53</v>
       </c>
@@ -1660,24 +1882,24 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I25" s="35" t="s">
+      <c r="I25" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="37"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="31"/>
     </row>
     <row r="26" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
       <c r="I26" s="7" t="s">
         <v>52</v>
       </c>
@@ -1755,14 +1977,14 @@
       <c r="G29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="35" t="s">
+      <c r="I29" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="37"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="31"/>
     </row>
     <row r="30" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I30" s="7" t="s">
@@ -1781,14 +2003,14 @@
       </c>
     </row>
     <row r="31" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
       <c r="I31" s="7" t="s">
         <v>68</v>
       </c>
@@ -1882,22 +2104,15 @@
     </row>
     <row r="35" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
+      <c r="L35" s="2"/>
     </row>
     <row r="36" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>40</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="J36" s="15" t="s">
+      <c r="J36" s="13" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1931,12 +2146,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="I29:N29"/>
-    <mergeCell ref="I25:N25"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="I10:N10"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B7:G7"/>
@@ -1945,6 +2154,12 @@
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="B4:G4"/>
+    <mergeCell ref="I29:N29"/>
+    <mergeCell ref="I25:N25"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="I10:N10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -1976,27 +2191,27 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="24" t="s">
-        <v>158</v>
+      <c r="B2" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="20" t="s">
+        <v>39</v>
       </c>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="26"/>
       <c r="I3" s="3"/>
       <c r="J3" s="11"/>
     </row>
@@ -2024,7 +2239,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="F6" s="10" t="s">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="O6" s="10"/>
     </row>
@@ -2044,1166 +2259,1404 @@
       <c r="O8" s="10"/>
     </row>
     <row r="9" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="J9" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+    </row>
+    <row r="10" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M10" s="21"/>
+      <c r="N10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="O10" s="5"/>
+      <c r="P10" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="21"/>
+      <c r="F11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M11" s="21"/>
+      <c r="N11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="O11" s="5"/>
+      <c r="P11" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="21"/>
+      <c r="H12" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O12" s="21"/>
+      <c r="P12" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O13" s="21"/>
+      <c r="P13" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="21"/>
+      <c r="H14" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O14" s="21"/>
+      <c r="P14" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="24">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="21"/>
+      <c r="H15" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O15" s="21"/>
+      <c r="P15" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="6"/>
+      <c r="H16" s="17"/>
+      <c r="L16" s="6"/>
+      <c r="P16" s="17"/>
+    </row>
+    <row r="17" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L17" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="J9" s="33" t="s">
+      <c r="M17" s="21"/>
+      <c r="N17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="O17" s="5"/>
+      <c r="P17" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="21"/>
+      <c r="F18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M18" s="21"/>
+      <c r="N18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="O18" s="5"/>
+      <c r="P18" s="17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="H19" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-    </row>
-    <row r="10" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="M19" s="21"/>
+      <c r="N19" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O19" s="21"/>
+      <c r="P19" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="21"/>
+      <c r="H20" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="K20" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="25">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="16">
-        <v>2</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="25">
-        <v>3</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="O10" s="16">
-        <v>0</v>
-      </c>
-      <c r="P10" s="21" t="s">
+      <c r="L20" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O20" s="21"/>
+      <c r="P20" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="J21" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O21" s="21"/>
+      <c r="P21" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O22" s="21"/>
+      <c r="P22" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="25">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="16">
-        <v>2</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L11" s="6" t="s">
+    <row r="23" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="D23" s="6"/>
+      <c r="H23" s="17"/>
+      <c r="L23" s="6"/>
+      <c r="P23" s="17"/>
+    </row>
+    <row r="24" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="M11" s="25">
-        <v>1</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="O11" s="16">
-        <v>1</v>
-      </c>
-      <c r="P11" s="21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="25">
-        <v>0</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="26">
-        <v>2</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" s="25">
-        <v>2</v>
-      </c>
-      <c r="N12" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O12" s="26">
-        <v>1</v>
-      </c>
-      <c r="P12" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="29">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="25">
-        <v>3</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="26">
-        <v>1</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="25">
-        <v>2</v>
-      </c>
-      <c r="N13" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O13" s="26">
-        <v>1</v>
-      </c>
-      <c r="P13" s="21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="25">
-        <v>2</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="26">
-        <v>0</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="J14" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="M14" s="25">
-        <v>1</v>
-      </c>
-      <c r="N14" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O14" s="26">
-        <v>1</v>
-      </c>
-      <c r="P14" s="21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="29">
-        <v>0.625</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="25">
-        <v>3</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="26">
-        <v>0</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="J15" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M15" s="25">
-        <v>2</v>
-      </c>
-      <c r="N15" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O15" s="26">
-        <v>2</v>
-      </c>
-      <c r="P15" s="21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" s="25">
-        <v>3</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="16">
-        <v>1</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J17" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" s="25">
-        <v>1</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="O17" s="16">
-        <v>1</v>
-      </c>
-      <c r="P17" s="21" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="29">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" s="25">
-        <v>2</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="16">
-        <v>1</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" s="25">
-        <v>3</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="O18" s="16">
-        <v>0</v>
-      </c>
-      <c r="P18" s="21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="25">
-        <v>0</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" s="26">
-        <v>1</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="M19" s="25">
-        <v>2</v>
-      </c>
-      <c r="N19" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O19" s="26">
-        <v>1</v>
-      </c>
-      <c r="P19" s="21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="25">
-        <v>2</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" s="26">
-        <v>2</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="J20" s="29">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M20" s="25">
-        <v>2</v>
-      </c>
-      <c r="N20" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O20" s="26">
-        <v>2</v>
-      </c>
-      <c r="P20" s="21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="25">
-        <v>1</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="26">
-        <v>2</v>
-      </c>
-      <c r="H21" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="M21" s="25">
-        <v>0</v>
-      </c>
-      <c r="N21" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O21" s="26">
-        <v>2</v>
-      </c>
-      <c r="P21" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="25">
-        <v>1</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="26">
-        <v>1</v>
-      </c>
-      <c r="H22" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="J22" s="29">
-        <v>0.625</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="M22" s="25">
-        <v>1</v>
-      </c>
-      <c r="N22" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O22" s="26">
-        <v>2</v>
-      </c>
-      <c r="P22" s="21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-    </row>
-    <row r="24" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
-      <c r="B24" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="25">
-        <v>2</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" s="25">
-        <v>0</v>
-      </c>
-      <c r="H24" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>106</v>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>133</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="M24" s="25">
-        <v>1</v>
-      </c>
-      <c r="N24" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O24" s="25">
-        <v>1</v>
-      </c>
-      <c r="P24" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O24" s="21"/>
+      <c r="P24" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="21"/>
+      <c r="H25" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J25" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O25" s="21"/>
+      <c r="P25" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="21"/>
+      <c r="H26" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O26" s="21"/>
+      <c r="P26" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12"/>
+      <c r="B27" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="21"/>
+      <c r="H27" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="J27" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O27" s="21"/>
+      <c r="P27" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12"/>
+      <c r="B28" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="21"/>
+      <c r="H28" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O28" s="21"/>
+      <c r="P28" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="21"/>
+      <c r="H29" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O29" s="21"/>
+      <c r="P29" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12"/>
+      <c r="D30" s="6"/>
+      <c r="H30" s="17"/>
+      <c r="L30" s="6"/>
+      <c r="P30" s="17"/>
+    </row>
+    <row r="31" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="21"/>
+      <c r="H31" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="J31" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O31" s="21"/>
+      <c r="P31" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="21"/>
+      <c r="H32" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="J32" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O32" s="21"/>
+      <c r="P32" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="21"/>
+      <c r="H33" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="J33" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O33" s="21"/>
+      <c r="P33" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12"/>
+      <c r="B34" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="21"/>
+      <c r="H34" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="J34" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M34" s="21"/>
+      <c r="N34" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O34" s="21"/>
+      <c r="P34" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12"/>
+      <c r="B35" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="21"/>
+      <c r="H35" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O35" s="21"/>
+      <c r="P35" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12"/>
+      <c r="B36" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="21"/>
+      <c r="H36" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="J36" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O36" s="21"/>
+      <c r="P36" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12"/>
+      <c r="D37" s="6"/>
+      <c r="H37" s="17"/>
+      <c r="L37" s="6"/>
+      <c r="P37" s="17"/>
+    </row>
+    <row r="38" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12"/>
+      <c r="B38" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="21"/>
+      <c r="H38" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="J38" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O38" s="21"/>
+      <c r="P38" s="17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+      <c r="B39" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="21"/>
+      <c r="H39" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="J39" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="21"/>
+      <c r="N39" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O39" s="21"/>
+      <c r="P39" s="17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="12"/>
+      <c r="B40" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="21"/>
+      <c r="H40" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="J40" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M40" s="21"/>
+      <c r="N40" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O40" s="21"/>
+      <c r="P40" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
+      <c r="B41" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="21"/>
+      <c r="H41" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="J41" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="M41" s="21"/>
+      <c r="N41" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O41" s="21"/>
+      <c r="P41" s="17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12"/>
+      <c r="B42" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="21"/>
+      <c r="H42" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="M42" s="21"/>
+      <c r="N42" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O42" s="21"/>
+      <c r="P42" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
+      <c r="B43" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="21"/>
+      <c r="H43" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="J43" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O43" s="21"/>
+      <c r="P43" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="12"/>
+      <c r="D44" s="6"/>
+      <c r="H44" s="17"/>
+      <c r="L44" s="6"/>
+      <c r="P44" s="17"/>
+    </row>
+    <row r="45" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+      <c r="B45" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="21"/>
+      <c r="H45" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="J45" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" s="21"/>
+      <c r="N45" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O45" s="21"/>
+      <c r="P45" s="17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
-      <c r="B25" s="29">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="25">
-        <v>2</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" s="25">
-        <v>0</v>
-      </c>
-      <c r="H25" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="J25" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M25" s="25">
-        <v>2</v>
-      </c>
-      <c r="N25" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O25" s="26">
-        <v>0</v>
-      </c>
-      <c r="P25" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
-      <c r="B26" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E26" s="25">
-        <v>1</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="26">
-        <v>1</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="J26" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M26" s="25">
-        <v>2</v>
-      </c>
-      <c r="N26" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O26" s="26">
-        <v>0</v>
-      </c>
-      <c r="P26" s="21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
-      <c r="B27" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="25">
-        <v>1</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" s="26">
-        <v>1</v>
-      </c>
-      <c r="H27" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" s="29">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L27" s="6" t="s">
+    <row r="46" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="12"/>
+      <c r="B46" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="21"/>
+      <c r="H46" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="J46" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M46" s="21"/>
+      <c r="N46" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O46" s="21"/>
+      <c r="P46" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="12"/>
+      <c r="B47" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="21"/>
+      <c r="H47" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="J47" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M47" s="21"/>
+      <c r="N47" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O47" s="21"/>
+      <c r="P47" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="12"/>
+      <c r="B48" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="21"/>
+      <c r="H48" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="J48" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="M48" s="21"/>
+      <c r="N48" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O48" s="21"/>
+      <c r="P48" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="M27" s="25">
-        <v>3</v>
-      </c>
-      <c r="N27" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O27" s="26">
-        <v>0</v>
-      </c>
-      <c r="P27" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
-      <c r="B28" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E28" s="25">
-        <v>0</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="26">
-        <v>2</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L28" s="6" t="s">
+    </row>
+    <row r="49" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="12"/>
+      <c r="B49" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="21"/>
+      <c r="H49" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O49" s="21"/>
+      <c r="P49" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="12"/>
+      <c r="B50" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="21"/>
+      <c r="H50" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="J50" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="M28" s="25">
-        <v>1</v>
-      </c>
-      <c r="N28" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O28" s="26">
-        <v>1</v>
-      </c>
-      <c r="P28" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
-      <c r="B29" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" s="25">
-        <v>0</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" s="26">
-        <v>2</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="J29" s="29">
-        <v>0.625</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M29" s="25">
-        <v>0</v>
-      </c>
-      <c r="N29" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O29" s="26">
-        <v>2</v>
-      </c>
-      <c r="P29" s="21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
-    </row>
-    <row r="31" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="25">
-        <v>1</v>
-      </c>
-      <c r="F31" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="26">
-        <v>1</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="J31" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="M31" s="25">
-        <v>2</v>
-      </c>
-      <c r="N31" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O31" s="26">
-        <v>0</v>
-      </c>
-      <c r="P31" s="21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E32" s="25">
-        <v>2</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" s="26">
-        <v>1</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="J32" s="29">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M32" s="25">
-        <v>3</v>
-      </c>
-      <c r="N32" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O32" s="26">
-        <v>1</v>
-      </c>
-      <c r="P32" s="21" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E33" s="25">
-        <v>1</v>
-      </c>
-      <c r="F33" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" s="26">
-        <v>2</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="J33" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="M33" s="25">
-        <v>1</v>
-      </c>
-      <c r="N33" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O33" s="26">
-        <v>1</v>
-      </c>
-      <c r="P33" s="21" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="29">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E34" s="25">
-        <v>2</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="26">
-        <v>0</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M34" s="25">
-        <v>1</v>
-      </c>
-      <c r="N34" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O34" s="26">
-        <v>1</v>
-      </c>
-      <c r="P34" s="21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="18"/>
-      <c r="B35" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" s="25">
-        <v>2</v>
-      </c>
-      <c r="F35" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G35" s="26">
-        <v>0</v>
-      </c>
-      <c r="H35" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="M35" s="25">
-        <v>1</v>
-      </c>
-      <c r="N35" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O35" s="26">
-        <v>2</v>
-      </c>
-      <c r="P35" s="21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="18"/>
-      <c r="B36" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E36" s="25">
-        <v>0</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" s="26">
-        <v>1</v>
-      </c>
-      <c r="H36" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="J36" s="29">
-        <v>0.625</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="M36" s="25">
-        <v>0</v>
-      </c>
-      <c r="N36" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="O36" s="26">
-        <v>2</v>
-      </c>
-      <c r="P36" s="21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="18"/>
-    </row>
-    <row r="38" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="18"/>
-    </row>
-    <row r="39" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="18"/>
-    </row>
-    <row r="40" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="18"/>
-    </row>
-    <row r="41" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="18"/>
-    </row>
-    <row r="42" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="18"/>
-    </row>
-    <row r="43" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="18"/>
-    </row>
-    <row r="44" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="18"/>
-    </row>
-    <row r="45" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="18"/>
-    </row>
-    <row r="46" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="18"/>
-    </row>
-    <row r="47" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="18"/>
-    </row>
-    <row r="48" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="18"/>
-    </row>
-    <row r="49" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="18"/>
-    </row>
-    <row r="50" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="18"/>
-    </row>
-    <row r="51" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="18"/>
-    </row>
-    <row r="52" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="18"/>
-    </row>
-    <row r="53" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="18"/>
-    </row>
-    <row r="54" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="18"/>
-    </row>
-    <row r="55" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="18"/>
-    </row>
-    <row r="56" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="18"/>
-    </row>
-    <row r="57" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="O50" s="21"/>
+      <c r="P50" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="12"/>
+    </row>
+    <row r="52" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="12"/>
+    </row>
+    <row r="53" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="12"/>
+    </row>
+    <row r="54" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="12"/>
+    </row>
+    <row r="55" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="12"/>
+    </row>
+    <row r="56" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="12"/>
+    </row>
+    <row r="57" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3218,7 +3671,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F75B2B-C704-4482-8312-FAE9069629EC}">
-  <dimension ref="A2:O28"/>
+  <dimension ref="A2:O37"/>
   <sheetFormatPr defaultRowHeight="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3229,24 +3682,24 @@
     <col min="6" max="6" width="9.140625" style="1"/>
     <col min="7" max="7" width="23.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="3.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.140625" style="1"/>
-    <col min="14" max="14" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.5703125" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="24" t="s">
+      <c r="B2" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="20" t="s">
         <v>39</v>
       </c>
       <c r="H2" s="3"/>
@@ -3260,39 +3713,39 @@
         <v>49</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N3" s="10"/>
     </row>
     <row r="4" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
+      <c r="B4" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="I4" s="9" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="27"/>
+        <v>73</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="22"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="21"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="17"/>
       <c r="I5" s="10" t="s">
         <v>41</v>
       </c>
@@ -3302,318 +3755,561 @@
     </row>
     <row r="6" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="29">
-        <v>0.79166666666666663</v>
+        <v>74</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>205</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="28"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="23"/>
       <c r="I6" s="10" t="s">
         <v>43</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="27"/>
+        <v>75</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" s="22"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="21"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="17"/>
       <c r="I7" s="10" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="29">
-        <v>0.79166666666666663</v>
+        <v>76</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>207</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="28"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="23"/>
       <c r="I8" s="10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="27"/>
+        <v>77</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" s="22"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="22"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C10" s="27"/>
+        <v>78</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="22"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="22"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="18"/>
       <c r="I10" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>143</v>
+        <v>79</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>210</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="28"/>
-      <c r="I11" s="17" t="s">
+      <c r="F11" s="5"/>
+      <c r="G11" s="23"/>
+      <c r="I11" s="14" t="s">
         <v>70</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="5">
         <v>1</v>
       </c>
-      <c r="N11" s="21" t="s">
-        <v>151</v>
+      <c r="N11" s="17" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>8</v>
-      </c>
-      <c r="B12" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C12" s="27"/>
+        <v>80</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" s="22"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="22"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="18"/>
+      <c r="I12" s="1" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="13" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>81</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="18"/>
       <c r="I13" s="1" t="s">
-        <v>159</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>82</v>
+      </c>
       <c r="B14" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <v>83</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="18"/>
+      <c r="I15" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <v>84</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <v>85</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <v>86</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="18"/>
+      <c r="I18" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="I14" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="31"/>
+    </row>
+    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>87</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="12">
+        <v>97</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="J19" s="19"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="M19" s="21"/>
+      <c r="N19" s="18"/>
+    </row>
+    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>88</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="12">
+        <v>98</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="J20" s="19"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="M20" s="21"/>
+      <c r="N20" s="18"/>
+    </row>
+    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="H21" s="12">
+        <v>99</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="J21" s="19"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="M21" s="21"/>
+      <c r="N21" s="18"/>
+    </row>
+    <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="12">
+        <v>100</v>
+      </c>
+      <c r="I22" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="J22" s="19"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="M22" s="21"/>
+      <c r="N22" s="18"/>
+    </row>
+    <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>89</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="17"/>
+    </row>
+    <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>90</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="25"/>
-      <c r="G15" s="22"/>
-    </row>
-    <row r="16" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="25"/>
-      <c r="G16" s="22"/>
-      <c r="I16" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F17" s="25"/>
-      <c r="G17" s="22"/>
-    </row>
-    <row r="18" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="22"/>
-    </row>
-    <row r="20" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-    </row>
-    <row r="21" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="24" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-    </row>
-    <row r="25" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C25" s="20"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="31"/>
+    </row>
+    <row r="25" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>91</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" s="22"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="19"/>
-    </row>
-    <row r="27" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-    </row>
-    <row r="28" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C28" s="20"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="12">
+        <v>101</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="J25" s="16"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="15"/>
+    </row>
+    <row r="26" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>92</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="12">
+        <v>102</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="J26" s="16"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="15"/>
+    </row>
+    <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>93</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="18"/>
+    </row>
+    <row r="28" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>94</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="22"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="19"/>
+      <c r="G28" s="18"/>
+      <c r="I28" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="31"/>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>95</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="1">
+        <v>103</v>
+      </c>
+      <c r="I29" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="J29" s="16"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="15"/>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>96</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="18"/>
+    </row>
+    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I31" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="31"/>
+    </row>
+    <row r="32" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H32" s="1">
+        <v>104</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="J32" s="16"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="15"/>
+    </row>
+    <row r="37" spans="1:1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B27:G27"/>
+  <mergeCells count="7">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="I28:N28"/>
+    <mergeCell ref="I31:N31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
